--- a/docs/0OMsoqOg9GiJ2xusVHMv/.gitbook/assets/IO - Template servizi - Trasporto scolastico .xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHMv/.gitbook/assets/IO - Template servizi - Trasporto scolastico .xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="107">
   <si>
     <r>
       <t xml:space="preserve">
@@ -903,8 +903,8 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
-Se hai già provveduto a pagare l'avviso ignora questo messaggio.
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+Se hai già provveduto a pagare l'avviso, ignora questo messaggio.
 Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
 In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
     </r>
@@ -960,10 +960,7 @@
     <t>Scopri tutte le agevolazioni</t>
   </si>
   <si>
-    <t>Vedi avviso</t>
-  </si>
-  <si>
-    <t>Vedi Avviso</t>
+    <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
   </si>
   <si>
     <r>
@@ -1789,12 +1786,12 @@
         <v>87</v>
       </c>
       <c r="H6" s="34" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>57</v>
@@ -1820,7 +1817,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>84</v>
@@ -1846,59 +1843,59 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="C9" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="D9" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="D9" s="34" t="s">
+      <c r="E9" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="F9" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="E9" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="F9" s="34" t="s">
+      <c r="G9" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="G9" s="34" t="s">
+      <c r="H9" s="34" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="H9" s="34" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+      <c r="B10" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="C10" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="D10" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="E10" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="F10" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="F10" s="34" t="s">
+      <c r="G10" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="G10" s="34" t="s">
+      <c r="H10" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="H10" s="34" t="s">
-        <v>104</v>
-      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>57</v>
@@ -1916,10 +1913,10 @@
         <v>57</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
